--- a/data/merged/2026-10-08/MERGED_DE_Mite-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_DE_Mite-Vacuum_2026-10-08.xlsx
@@ -5867,13 +5867,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5911,13 +5911,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6276,7 +6276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16473,40 +16473,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H3WC9R3Y</t>
+          <t>B0D5LDYQFZ</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/stores/CLEANmaxx/page/506A1067-8CB3-4B2C-91D5-F17131B49546?lp_asin=B0H3WC9R3Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.de/stores/JIGOOMilbensauger/page/AEFA4A1B-1A4A-42B0-8E3A-01D20DDFB20B?lp_asin=B0D5LDYQFZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx Polsterreiniger Gerät Kompakt ProsNasssauger &amp; Teppichreiniger in einem | 13 kPa Waschsauger für Polster &amp; Autosi</t>
+          <t>JIGOO T600 Milbensauger für matratzen, 700W Milbenstaubsauger mit UV Licht, 15kpa Anziehung Milben Staubsauger Antimilben-Sta</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0H3WC9R3Y?psc=1</t>
+          <t>https://www.amazon.de/dp/B0D5LDYQFZ?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41IERHDEQRL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71eCqjKmW3L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H3WC9R3Y</t>
+          <t>B0D5LDYQFZ</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -16520,13 +16520,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>164586</v>
+        <v>904423</v>
       </c>
       <c r="P45" s="15">
-        <v>524219</v>
+        <v>-55875</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.79</v>
+        <v>-0.07</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -16535,89 +16535,83 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>104</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>11</v>
-      </c>
-      <c r="U45" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="U45" s="16">
+        <v>0</v>
+      </c>
       <c r="V45" s="15">
-        <v>550</v>
+        <v>459</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
       <c r="Y45" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z45" s="20">
-        <v>49.99</v>
+        <v>144.43</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE45" s="15"/>
+        <v>826</v>
+      </c>
+      <c r="AE45" s="15">
+        <v>21</v>
+      </c>
       <c r="AF45" s="21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG45" s="22">
         <v>0</v>
       </c>
       <c r="AH45" s="20">
-        <v>5.29</v>
+        <v>5.08</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>125</v>
+        <v>851</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45"/>
-      <c r="AQ45" s="19"/>
+      <c r="AQ45" s="19">
+        <v>10</v>
+      </c>
       <c r="AR45" s="19">
         <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>DS e-Sales GmbH</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU45" s="13" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="AV45" s="14" t="inlineStr">
-        <is>
-          <t>Stapelfeld 22145 DE</t>
-        </is>
-      </c>
-      <c r="AW45" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU45" s="13"/>
+      <c r="AV45" s="14"/>
+      <c r="AW45" s="13"/>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
@@ -16628,7 +16622,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13"/>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
@@ -16636,34 +16634,42 @@
       <c r="BI45" s="23"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>3,4 Kilograms</t>
+          <t>2.97 kg</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
-        </is>
-      </c>
-      <c r="BL45" s="23"/>
-      <c r="BM45" s="23"/>
+          <t>2.97 kg</t>
+        </is>
+      </c>
+      <c r="BL45" s="23" t="inlineStr">
+        <is>
+          <t>28 x 28 x 24 cm</t>
+        </is>
+      </c>
+      <c r="BM45" s="23" t="inlineStr">
+        <is>
+          <t>28.00 x 28.00 x 24.00 cm</t>
+        </is>
+      </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>3.4 kg</t>
+          <t>2.97 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
+          <t>2.97 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>35.5 x 30.5 x 19.5 cm</t>
+          <t>37.5 x 30.1 x 25.1 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>35.50 x 30.50 x 19.50 cm</t>
+          <t>37.50 x 30.10 x 25.10 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
@@ -16679,40 +16685,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0D5LDYQFZ</t>
+          <t>B0H8XNCYS3</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Umllpet</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/stores/JIGOOMilbensauger/page/AEFA4A1B-1A4A-42B0-8E3A-01D20DDFB20B?lp_asin=B0D5LDYQFZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.de/stores/Umllpet/page/1C0BF92A-ED68-4D40-AF22-E09660C6FCA2?lp_asin=B0H8XNCYS3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Milbensauger für matratzen, 700W Milbenstaubsauger mit UV Licht, 15kpa Anziehung Milben Staubsauger Antimilben-Sta</t>
+          <t>Milbensauger für Matratzen UV-C Licht 20kPa Handstaubsauger mit HEPA Filters253,7 nm UV Sterilisation, starke 20kPa Saugkra</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0D5LDYQFZ?psc=1</t>
+          <t>https://www.amazon.de/dp/B0H8XNCYS3?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71eCqjKmW3L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/6195obguLuL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0D5LDYQFZ</t>
+          <t>B0H8XNCYS3</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -16726,13 +16732,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>904423</v>
+        <v>183498</v>
       </c>
       <c r="P46" s="15">
-        <v>-55875</v>
+        <v>227058</v>
       </c>
       <c r="Q46" s="16">
-        <v>-0.07</v>
+        <v>0.3</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -16741,98 +16747,94 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>3</v>
-      </c>
-      <c r="U46" s="16">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>459</v>
+        <v>156</v>
       </c>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>144.43</v>
+        <v>25.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
-      <c r="AD46" s="19">
-        <v>826</v>
-      </c>
-      <c r="AE46" s="15">
-        <v>21</v>
-      </c>
-      <c r="AF46" s="21">
-        <v>4.6</v>
-      </c>
+      <c r="AD46" s="19"/>
+      <c r="AE46" s="15"/>
+      <c r="AF46" s="21"/>
       <c r="AG46" s="22">
         <v>0</v>
       </c>
       <c r="AH46" s="20">
-        <v>5.08</v>
+        <v>3.56</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>851</v>
+        <v>43</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AR46" s="19">
         <v>1</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Umllpet</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>Shenzhen Guangdong 518000 CN</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC46" s="13"/>
+      <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
@@ -16840,47 +16842,47 @@
       <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>2.97 kg</t>
+          <t>650 g</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>2.97 kg</t>
+          <t>650.00 g</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>28 x 28 x 24 cm</t>
+          <t>25 x 20.4 x 11 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>28.00 x 28.00 x 24.00 cm</t>
+          <t>25.00 x 20.40 x 11.00 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>2.97 kg</t>
+          <t>650 g</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>2.97 kg</t>
+          <t>650.00 g</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>37.5 x 30.1 x 25.1 cm</t>
+          <t>25 x 20.4 x 11 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>37.50 x 30.10 x 25.10 cm</t>
+          <t>25.00 x 20.40 x 11.00 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -16891,149 +16893,85 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H8XNCYS3</t>
+          <t>B07Y3CDHQ7</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>Umllpet</t>
-        </is>
-      </c>
+      <c r="F47" s="14"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/stores/Umllpet/page/1C0BF92A-ED68-4D40-AF22-E09660C6FCA2?lp_asin=B0H8XNCYS3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.deundefined</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Milbensauger für Matratzen UV-C Licht 20kPa Handstaubsauger mit HEPA Filters253,7 nm UV Sterilisation, starke 20kPa Saugkra</t>
+          <t>Brandson - Milbenstaubsauger 300W - Matratzensauger Milbensauger mit UV Sterilisationslicht - Schmutzbehälter 150 ml - desinf</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0H8XNCYS3?psc=1</t>
+          <t>https://www.amazon.de/dp/B07Y3CDHQ7?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/6195obguLuL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71p3zlwt6GL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H8XNCYS3</t>
-        </is>
-      </c>
-      <c r="M47" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen:Haushaltsreiniger &amp; Staubsauger:Staubsauger:Matratzensauger</t>
-        </is>
-      </c>
-      <c r="N47" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen</t>
-        </is>
-      </c>
-      <c r="O47" s="15">
-        <v>183498</v>
-      </c>
-      <c r="P47" s="15">
-        <v>227058</v>
-      </c>
-      <c r="Q47" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="R47" s="17" t="inlineStr">
-        <is>
-          <t>Matratzensauger</t>
-        </is>
-      </c>
-      <c r="S47" s="18" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="T47" s="15">
-        <v>6</v>
-      </c>
+          <t>B07Y3CDHQ7</t>
+        </is>
+      </c>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="15"/>
       <c r="U47" s="16"/>
-      <c r="V47" s="15">
-        <v>156</v>
-      </c>
+      <c r="V47" s="15"/>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
-      <c r="Y47" s="19">
-        <v>1</v>
-      </c>
+      <c r="Y47" s="19"/>
       <c r="Z47" s="20">
-        <v>25.99</v>
+        <v>28.24</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="2"/>
-      <c r="AD47" s="19"/>
+      <c r="AD47" s="19">
+        <v>491</v>
+      </c>
       <c r="AE47" s="15"/>
-      <c r="AF47" s="21"/>
+      <c r="AF47" s="21">
+        <v>4.2</v>
+      </c>
       <c r="AG47" s="22">
         <v>0</v>
       </c>
-      <c r="AH47" s="20">
-        <v>3.56</v>
-      </c>
+      <c r="AH47" s="20"/>
       <c r="AI47" s="16">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
-      <c r="AK47" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AL47" s="19">
-        <v>43</v>
-      </c>
-      <c r="AM47" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK47" s="13"/>
+      <c r="AL47" s="19"/>
+      <c r="AM47" s="13"/>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
-      <c r="AQ47" s="19">
-        <v>6</v>
-      </c>
-      <c r="AR47" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS47" s="14" t="inlineStr">
-        <is>
-          <t>Umllpet</t>
-        </is>
-      </c>
-      <c r="AT47" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>Shenzhen Guangdong 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW47" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804</t>
-        </is>
-      </c>
+      <c r="AQ47" s="19"/>
+      <c r="AR47" s="19"/>
+      <c r="AS47" s="14"/>
+      <c r="AT47" s="13"/>
+      <c r="AU47" s="13"/>
+      <c r="AV47" s="14"/>
+      <c r="AW47" s="13"/>
       <c r="AX47" s="13"/>
       <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
@@ -17046,51 +16984,15 @@
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
       <c r="BI47" s="23"/>
-      <c r="BJ47" s="23" t="inlineStr">
-        <is>
-          <t>650 g</t>
-        </is>
-      </c>
-      <c r="BK47" s="23" t="inlineStr">
-        <is>
-          <t>650.00 g</t>
-        </is>
-      </c>
-      <c r="BL47" s="23" t="inlineStr">
-        <is>
-          <t>25 x 20.4 x 11 cm</t>
-        </is>
-      </c>
-      <c r="BM47" s="23" t="inlineStr">
-        <is>
-          <t>25.00 x 20.40 x 11.00 cm</t>
-        </is>
-      </c>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>650 g</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>650.00 g</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>25 x 20.4 x 11 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>25.00 x 20.40 x 11.00 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
+      <c r="BJ47" s="23"/>
+      <c r="BK47" s="23"/>
+      <c r="BL47" s="23"/>
+      <c r="BM47" s="23"/>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -17099,138 +17001,80 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
+          <t>B0D9BQHSWQ</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>KÄRCHER</t>
-        </is>
-      </c>
+      <c r="F48" s="14"/>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0GH912PFJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.deundefined</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER Filter-Set für VCH 4 UVClean Matratzenreiniger, Ersatzfilter aus Motorschutzfilter und Schaumfilter für hygienische R</t>
+          <t>Jimmy Milbensauger für Matratzen 15kPa Matratzensauger mit Staubsensor, Heißluftfunktion, UV-C Licht, Ultraschall-Technik, Mi</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0GH912PFJ?psc=1</t>
+          <t>https://www.amazon.de/dp/B0D9BQHSWQ?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51GeVSsTnnL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/619CHOWba4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
-        </is>
-      </c>
-      <c r="M48" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen:Haushaltsreiniger &amp; Staubsauger:Staubsauger:Matratzensauger</t>
-        </is>
-      </c>
-      <c r="N48" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen</t>
-        </is>
-      </c>
-      <c r="O48" s="15">
-        <v>137160</v>
-      </c>
-      <c r="P48" s="15">
-        <v>737201</v>
-      </c>
-      <c r="Q48" s="16">
-        <v>0.88</v>
-      </c>
-      <c r="R48" s="17" t="inlineStr">
-        <is>
-          <t>Matratzensauger</t>
-        </is>
-      </c>
-      <c r="S48" s="18" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="T48" s="15">
-        <v>6</v>
-      </c>
+          <t>B0D9BQHSWQ</t>
+        </is>
+      </c>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="15"/>
       <c r="U48" s="16"/>
-      <c r="V48" s="15">
-        <v>60</v>
-      </c>
+      <c r="V48" s="15"/>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
-      <c r="Y48" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z48" s="20">
-        <v>9.43</v>
-      </c>
+      <c r="Y48" s="19"/>
+      <c r="Z48" s="20"/>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE48" s="15">
-        <v>0</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AE48" s="15"/>
       <c r="AF48" s="21">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
       </c>
-      <c r="AH48" s="20">
-        <v>3.08</v>
-      </c>
+      <c r="AH48" s="20"/>
       <c r="AI48" s="16">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AJ48"/>
-      <c r="AK48" s="13" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AL48" s="19">
-        <v>240</v>
-      </c>
-      <c r="AM48" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK48" s="13"/>
+      <c r="AL48" s="19"/>
+      <c r="AM48" s="13"/>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19"/>
-      <c r="AR48" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS48" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT48" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AR48" s="19"/>
+      <c r="AS48" s="14"/>
+      <c r="AT48" s="13"/>
       <c r="AU48" s="13"/>
       <c r="AV48" s="14"/>
       <c r="AW48" s="13"/>
@@ -17246,51 +17090,15 @@
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
       <c r="BI48" s="23"/>
-      <c r="BJ48" s="23" t="inlineStr">
-        <is>
-          <t>10 g</t>
-        </is>
-      </c>
-      <c r="BK48" s="23" t="inlineStr">
-        <is>
-          <t>10.00 g</t>
-        </is>
-      </c>
-      <c r="BL48" s="23" t="inlineStr">
-        <is>
-          <t>6.4 x 3.2 x 5 cm</t>
-        </is>
-      </c>
-      <c r="BM48" s="23" t="inlineStr">
-        <is>
-          <t>6.40 x 3.20 x 5.00 cm</t>
-        </is>
-      </c>
-      <c r="BN48" s="23" t="inlineStr">
-        <is>
-          <t>20 g</t>
-        </is>
-      </c>
-      <c r="BO48" s="23" t="inlineStr">
-        <is>
-          <t>20.00 g</t>
-        </is>
-      </c>
-      <c r="BP48" s="23" t="inlineStr">
-        <is>
-          <t>9.6 x 6.6 x 4.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ48" s="23" t="inlineStr">
-        <is>
-          <t>9.60 x 6.60 x 4.70 cm</t>
-        </is>
-      </c>
-      <c r="BR48" s="13" t="inlineStr">
-        <is>
-          <t>超大号信封</t>
-        </is>
-      </c>
+      <c r="BJ48" s="23"/>
+      <c r="BK48" s="23"/>
+      <c r="BL48" s="23"/>
+      <c r="BM48" s="23"/>
+      <c r="BN48" s="23"/>
+      <c r="BO48" s="23"/>
+      <c r="BP48" s="23"/>
+      <c r="BQ48" s="23"/>
+      <c r="BR48" s="13"/>
     </row>
     <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -17299,7 +17107,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B07Y3CDHQ7</t>
+          <t>B0H94CDXYP</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -17312,23 +17120,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Brandson - Milbenstaubsauger 300W - Matratzensauger Milbensauger mit UV Sterilisationslicht - Schmutzbehälter 150 ml - desinf</t>
+          <t>Lubluelu Milbensauger 22 kPa, Staub- &amp; Milbenerkennung, 70 °C HeißluftsMatratzensauger, 65.000 Schläge/min, UV-C, Duftfunkt</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B07Y3CDHQ7?psc=1</t>
+          <t>https://www.amazon.de/dp/B0H94CDXYP?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71p3zlwt6GL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Qj+s7NeNL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B07Y3CDHQ7</t>
+          <t>B0H94CDXYP</t>
         </is>
       </c>
       <c r="M49" s="14"/>
@@ -17344,19 +17152,13 @@
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
       <c r="Y49" s="19"/>
-      <c r="Z49" s="20">
-        <v>28.24</v>
-      </c>
+      <c r="Z49" s="20"/>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="2"/>
-      <c r="AD49" s="19">
-        <v>491</v>
-      </c>
+      <c r="AD49" s="19"/>
       <c r="AE49" s="15"/>
-      <c r="AF49" s="21">
-        <v>4.2</v>
-      </c>
+      <c r="AF49" s="21"/>
       <c r="AG49" s="22">
         <v>0</v>
       </c>
@@ -17399,214 +17201,6 @@
       <c r="BP49" s="23"/>
       <c r="BQ49" s="23"/>
       <c r="BR49" s="13"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0D9BQHSWQ</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.deundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>Jimmy Milbensauger für Matratzen 15kPa Matratzensauger mit Staubsensor, Heißluftfunktion, UV-C Licht, Ultraschall-Technik, Mi</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/dp/B0D9BQHSWQ?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/619CHOWba4L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0D9BQHSWQ</t>
-        </is>
-      </c>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19"/>
-      <c r="Z50" s="20"/>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>139</v>
-      </c>
-      <c r="AE50" s="15"/>
-      <c r="AF50" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13"/>
-      <c r="AL50" s="19"/>
-      <c r="AM50" s="13"/>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19"/>
-      <c r="AR50" s="19"/>
-      <c r="AS50" s="14"/>
-      <c r="AT50" s="13"/>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23"/>
-      <c r="BK50" s="23"/>
-      <c r="BL50" s="23"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50" s="23"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50" s="23"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H94CDXYP</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.deundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Milbensauger 22 kPa, Staub- &amp; Milbenerkennung, 70 °C HeißluftsMatratzensauger, 65.000 Schläge/min, UV-C, Duftfunkt</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/dp/B0H94CDXYP?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Qj+s7NeNL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0H94CDXYP</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19"/>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21"/>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17948,53 +17542,38 @@
     <hyperlink ref="M44" r:id="rId334" tooltip="https://www.amazon.de/b?node=13528288031"/>
     <hyperlink ref="N44" r:id="rId335"/>
     <hyperlink ref="AW44" r:id="rId336" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DJZ6ZEQ14JUA"/>
-    <hyperlink ref="C45" r:id="rId337" tooltip="https://www.amazon.de/dp/B0H3WC9R3Y"/>
-    <hyperlink ref="G45" r:id="rId338" tooltip="https://www.amazon.de/stores/CLEANmaxx/page/506A1067-8CB3-4B2C-91D5-F17131B49546?lp_asin=B0H3WC9R3Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J45" r:id="rId339" tooltip="https://www.amazon.de/dp/B0H3WC9R3Y?psc=1"/>
-    <hyperlink ref="K45" r:id="rId340" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41IERHDEQRL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId341" tooltip="https://www.amazon.de/dp/B0H3WC9R3Y"/>
+    <hyperlink ref="C45" r:id="rId337" tooltip="https://www.amazon.de/dp/B0D5LDYQFZ"/>
+    <hyperlink ref="G45" r:id="rId338" tooltip="https://www.amazon.de/stores/JIGOOMilbensauger/page/AEFA4A1B-1A4A-42B0-8E3A-01D20DDFB20B?lp_asin=B0D5LDYQFZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId339" tooltip="https://www.amazon.de/dp/B0D5LDYQFZ?psc=1"/>
+    <hyperlink ref="K45" r:id="rId340" tooltip="https://images-na.ssl-images-amazon.com/images/I/71eCqjKmW3L._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId341" tooltip="https://www.amazon.de/dp/B0D5LDYQFZ"/>
     <hyperlink ref="M45" r:id="rId342" tooltip="https://www.amazon.de/b?node=13528288031"/>
     <hyperlink ref="N45" r:id="rId343"/>
-    <hyperlink ref="AW45" r:id="rId344" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K"/>
-    <hyperlink ref="C46" r:id="rId345" tooltip="https://www.amazon.de/dp/B0D5LDYQFZ"/>
-    <hyperlink ref="G46" r:id="rId346" tooltip="https://www.amazon.de/stores/JIGOOMilbensauger/page/AEFA4A1B-1A4A-42B0-8E3A-01D20DDFB20B?lp_asin=B0D5LDYQFZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId347" tooltip="https://www.amazon.de/dp/B0D5LDYQFZ?psc=1"/>
-    <hyperlink ref="K46" r:id="rId348" tooltip="https://images-na.ssl-images-amazon.com/images/I/71eCqjKmW3L._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId349" tooltip="https://www.amazon.de/dp/B0D5LDYQFZ"/>
-    <hyperlink ref="M46" r:id="rId350" tooltip="https://www.amazon.de/b?node=13528288031"/>
-    <hyperlink ref="N46" r:id="rId351"/>
-    <hyperlink ref="C47" r:id="rId352" tooltip="https://www.amazon.de/dp/B0H8XNCYS3"/>
-    <hyperlink ref="G47" r:id="rId353" tooltip="https://www.amazon.de/stores/Umllpet/page/1C0BF92A-ED68-4D40-AF22-E09660C6FCA2?lp_asin=B0H8XNCYS3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J47" r:id="rId354" tooltip="https://www.amazon.de/dp/B0H8XNCYS3?psc=1"/>
-    <hyperlink ref="K47" r:id="rId355" tooltip="https://images-na.ssl-images-amazon.com/images/I/6195obguLuL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId356" tooltip="https://www.amazon.de/dp/B0H8XNCYS3"/>
-    <hyperlink ref="M47" r:id="rId357" tooltip="https://www.amazon.de/b?node=13528288031"/>
-    <hyperlink ref="N47" r:id="rId358"/>
-    <hyperlink ref="AW47" r:id="rId359" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804"/>
-    <hyperlink ref="C48" r:id="rId360" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
-    <hyperlink ref="G48" r:id="rId361" tooltip="https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0GH912PFJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId362" tooltip="https://www.amazon.de/dp/B0GH912PFJ?psc=1"/>
-    <hyperlink ref="K48" r:id="rId363" tooltip="https://m.media-amazon.com/images/I/51GeVSsTnnL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId364" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
-    <hyperlink ref="M48" r:id="rId365" tooltip="https://www.amazon.de/b?node=13528288031"/>
-    <hyperlink ref="N48" r:id="rId366"/>
-    <hyperlink ref="C49" r:id="rId367" tooltip="https://www.amazon.de/dp/B07Y3CDHQ7"/>
-    <hyperlink ref="G49" r:id="rId368" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J49" r:id="rId369" tooltip="https://www.amazon.de/dp/B07Y3CDHQ7?psc=1"/>
-    <hyperlink ref="K49" r:id="rId370" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71p3zlwt6GL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId371" tooltip="https://www.amazon.de/dp/B07Y3CDHQ7"/>
-    <hyperlink ref="C50" r:id="rId372" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="G50" r:id="rId373" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J50" r:id="rId374" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId375" tooltip="https://images-eu.ssl-images-amazon.com/images/I/619CHOWba4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId376" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="C51" r:id="rId377" tooltip="https://www.amazon.de/dp/B0H94CDXYP"/>
-    <hyperlink ref="G51" r:id="rId378" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J51" r:id="rId379" tooltip="https://www.amazon.de/dp/B0H94CDXYP?psc=1"/>
-    <hyperlink ref="K51" r:id="rId380" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Qj+s7NeNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId381" tooltip="https://www.amazon.de/dp/B0H94CDXYP"/>
+    <hyperlink ref="C46" r:id="rId344" tooltip="https://www.amazon.de/dp/B0H8XNCYS3"/>
+    <hyperlink ref="G46" r:id="rId345" tooltip="https://www.amazon.de/stores/Umllpet/page/1C0BF92A-ED68-4D40-AF22-E09660C6FCA2?lp_asin=B0H8XNCYS3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J46" r:id="rId346" tooltip="https://www.amazon.de/dp/B0H8XNCYS3?psc=1"/>
+    <hyperlink ref="K46" r:id="rId347" tooltip="https://images-na.ssl-images-amazon.com/images/I/6195obguLuL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId348" tooltip="https://www.amazon.de/dp/B0H8XNCYS3"/>
+    <hyperlink ref="M46" r:id="rId349" tooltip="https://www.amazon.de/b?node=13528288031"/>
+    <hyperlink ref="N46" r:id="rId350"/>
+    <hyperlink ref="AW46" r:id="rId351" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804"/>
+    <hyperlink ref="C47" r:id="rId352" tooltip="https://www.amazon.de/dp/B07Y3CDHQ7"/>
+    <hyperlink ref="G47" r:id="rId353" tooltip="https://www.amazon.deundefined"/>
+    <hyperlink ref="J47" r:id="rId354" tooltip="https://www.amazon.de/dp/B07Y3CDHQ7?psc=1"/>
+    <hyperlink ref="K47" r:id="rId355" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71p3zlwt6GL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId356" tooltip="https://www.amazon.de/dp/B07Y3CDHQ7"/>
+    <hyperlink ref="C48" r:id="rId357" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
+    <hyperlink ref="G48" r:id="rId358" tooltip="https://www.amazon.deundefined"/>
+    <hyperlink ref="J48" r:id="rId359" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ?psc=1"/>
+    <hyperlink ref="K48" r:id="rId360" tooltip="https://images-eu.ssl-images-amazon.com/images/I/619CHOWba4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId361" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
+    <hyperlink ref="C49" r:id="rId362" tooltip="https://www.amazon.de/dp/B0H94CDXYP"/>
+    <hyperlink ref="G49" r:id="rId363" tooltip="https://www.amazon.deundefined"/>
+    <hyperlink ref="J49" r:id="rId364" tooltip="https://www.amazon.de/dp/B0H94CDXYP?psc=1"/>
+    <hyperlink ref="K49" r:id="rId365" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Qj+s7NeNL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId366" tooltip="https://www.amazon.de/dp/B0H94CDXYP"/>
   </hyperlinks>
-  <drawing r:id="rId382"/>
+  <drawing r:id="rId367"/>
 </worksheet>
 </file>
 
@@ -18064,7 +17643,7 @@
         <v>111.14432989690722</v>
       </c>
       <c r="G2" s="22">
-        <v>0.12309644670050761</v>
+        <v>0.12330106580619928</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18085,7 +17664,7 @@
         <v>120.70924690181126</v>
       </c>
       <c r="G3" s="22">
-        <v>0.10240140570089809</v>
+        <v>0.10257162413219909</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18106,7 +17685,7 @@
         <v>69.9900284900285</v>
       </c>
       <c r="G4" s="22">
-        <v>0.13705583756345177</v>
+        <v>0.13728366089762395</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18127,7 +17706,7 @@
         <v>88.05205811138015</v>
       </c>
       <c r="G5" s="22">
-        <v>0.080632565404139</v>
+        <v>0.08076659822039699</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18137,18 +17716,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C6" s="15">
-        <v>70694</v>
+        <v>70634</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>89.37294563843237</v>
+        <v>89.9796178343949</v>
       </c>
       <c r="G6" s="22">
-        <v>0.07721593127684498</v>
+        <v>0.07675760242495355</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18169,7 +17748,7 @@
         <v>70.5901287553648</v>
       </c>
       <c r="G7" s="22">
-        <v>0.09098008590394377</v>
+        <v>0.09113131905739709</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18179,18 +17758,18 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="C8" s="15">
-        <v>33845</v>
+        <v>33295</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="20">
-        <v>35.07253886010363</v>
+        <v>34.90041928721174</v>
       </c>
       <c r="G8" s="22">
-        <v>0.09420148379539242</v>
+        <v>0.09328248753300088</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18211,7 +17790,7 @@
         <v>67.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.04080437329168294</v>
+        <v>0.040872201036472086</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18232,7 +17811,7 @@
         <v>69.0</v>
       </c>
       <c r="G10" s="22">
-        <v>0.03465443186255369</v>
+        <v>0.03471203676542486</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18253,7 +17832,7 @@
         <v>50.68535825545171</v>
       </c>
       <c r="G11" s="22">
-        <v>0.03133541585318235</v>
+        <v>0.031387503666764446</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18274,7 +17853,7 @@
         <v>54.27838827838828</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0266497461928934</v>
+        <v>0.026694045174537988</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18295,7 +17874,7 @@
         <v>85.48818897637796</v>
       </c>
       <c r="G13" s="22">
-        <v>0.01239750097618118</v>
+        <v>0.012418108927349174</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18316,7 +17895,7 @@
         <v>100.82828282828282</v>
       </c>
       <c r="G14" s="22">
-        <v>0.009664193674345959</v>
+        <v>0.009680258140217073</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18337,7 +17916,7 @@
         <v>61.35897435897436</v>
       </c>
       <c r="G15" s="22">
-        <v>0.015228426395939087</v>
+        <v>0.015253740099735994</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18358,7 +17937,7 @@
         <v>117.5625</v>
       </c>
       <c r="G16" s="22">
-        <v>0.007809449433814916</v>
+        <v>0.007822430820377433</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18379,7 +17958,7 @@
         <v>99.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.008980866848887154</v>
+        <v>0.008995795443434047</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18400,7 +17979,7 @@
         <v>210.07692307692307</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0038071065989847717</v>
+        <v>0.0038134350249339984</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18421,7 +18000,7 @@
         <v>64.9908256880734</v>
       </c>
       <c r="G19" s="22">
-        <v>0.010640374853572823</v>
+        <v>0.010658061992764251</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18442,7 +18021,7 @@
         <v>99.98550724637681</v>
       </c>
       <c r="G20" s="22">
-        <v>0.006735650136665365</v>
+        <v>0.0067468465825755355</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18463,7 +18042,7 @@
         <v>42.54304635761589</v>
       </c>
       <c r="G21" s="22">
-        <v>0.014740335806325654</v>
+        <v>0.014764838173462403</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18484,7 +18063,7 @@
         <v>31.58011049723757</v>
       </c>
       <c r="G22" s="22">
-        <v>0.01766887934400625</v>
+        <v>0.01769824973110394</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18505,7 +18084,7 @@
         <v>99.98245614035088</v>
       </c>
       <c r="G23" s="22">
-        <v>0.005564232721593128</v>
+        <v>0.005573481959518921</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18526,7 +18105,7 @@
         <v>69.98529411764706</v>
       </c>
       <c r="G24" s="22">
-        <v>0.006638032018742679</v>
+        <v>0.006649066197320817</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18547,7 +18126,7 @@
         <v>28.97841726618705</v>
       </c>
       <c r="G25" s="22">
-        <v>0.013568918391253416</v>
+        <v>0.013591473550405788</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18568,7 +18147,7 @@
         <v>84.02127659574468</v>
       </c>
       <c r="G26" s="22">
-        <v>0.004588051542366263</v>
+        <v>0.004595678106971741</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18589,7 +18168,7 @@
         <v>59.983333333333334</v>
       </c>
       <c r="G27" s="22">
-        <v>0.005857087075361187</v>
+        <v>0.005866823115283074</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18610,7 +18189,7 @@
         <v>69.91111111111111</v>
       </c>
       <c r="G28" s="22">
-        <v>0.004392815306520891</v>
+        <v>0.004400117336462305</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18631,7 +18210,7 @@
         <v>80.0</v>
       </c>
       <c r="G29" s="22">
-        <v>0.0029285435376805937</v>
+        <v>0.002933411557641537</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18652,7 +18231,7 @@
         <v>66.5</v>
       </c>
       <c r="G30" s="22">
-        <v>0.001952362358453729</v>
+        <v>0.001955607705094358</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18673,7 +18252,7 @@
         <v>33.0</v>
       </c>
       <c r="G31" s="22">
-        <v>0.0031237797735259665</v>
+        <v>0.003128972328150973</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18694,7 +18273,7 @@
         <v>60.0</v>
       </c>
       <c r="G32" s="22">
-        <v>0.0016595080046856697</v>
+        <v>0.0016622665493302043</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18715,7 +18294,7 @@
         <v>28.0</v>
       </c>
       <c r="G33" s="22">
-        <v>0.0024404529480671613</v>
+        <v>0.0024445096313679476</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18736,7 +18315,7 @@
         <v>26.0</v>
       </c>
       <c r="G34" s="22">
-        <v>0.0005857087075361187</v>
+        <v>0.0005866823115283074</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18819,18 +18398,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>4119</v>
+        <v>4113</v>
       </c>
       <c r="C2" s="15">
-        <v>341294</v>
+        <v>341234</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>82.85846079145423</v>
+        <v>82.9647459275468</v>
       </c>
       <c r="G2" s="22">
-        <v>0.4020890277235455</v>
+        <v>0.40217072455265473</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18851,7 +18430,7 @@
         <v>121.35138248847926</v>
       </c>
       <c r="G3" s="22">
-        <v>0.08473252635689184</v>
+        <v>0.08487337440109514</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18872,7 +18451,7 @@
         <v>69.9900284900285</v>
       </c>
       <c r="G4" s="22">
-        <v>0.13705583756345177</v>
+        <v>0.13728366089762395</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18893,7 +18472,7 @@
         <v>70.5901287553648</v>
       </c>
       <c r="G5" s="22">
-        <v>0.09098008590394377</v>
+        <v>0.09113131905739709</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18914,7 +18493,7 @@
         <v>67.0</v>
       </c>
       <c r="G6" s="22">
-        <v>0.04080437329168294</v>
+        <v>0.040872201036472086</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18935,7 +18514,7 @@
         <v>69.0</v>
       </c>
       <c r="G7" s="22">
-        <v>0.03465443186255369</v>
+        <v>0.03471203676542486</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18956,7 +18535,7 @@
         <v>50.68535825545171</v>
       </c>
       <c r="G8" s="22">
-        <v>0.03133541585318235</v>
+        <v>0.031387503666764446</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18977,7 +18556,7 @@
         <v>69.9880239520958</v>
       </c>
       <c r="G9" s="22">
-        <v>0.01630222569308864</v>
+        <v>0.01632932433753789</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18998,7 +18577,7 @@
         <v>85.48818897637796</v>
       </c>
       <c r="G10" s="22">
-        <v>0.01239750097618118</v>
+        <v>0.012418108927349174</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19019,7 +18598,7 @@
         <v>100.82828282828282</v>
       </c>
       <c r="G11" s="22">
-        <v>0.009664193674345959</v>
+        <v>0.009680258140217073</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19040,7 +18619,7 @@
         <v>61.35897435897436</v>
       </c>
       <c r="G12" s="22">
-        <v>0.015228426395939087</v>
+        <v>0.015253740099735994</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19061,7 +18640,7 @@
         <v>117.5625</v>
       </c>
       <c r="G13" s="22">
-        <v>0.007809449433814916</v>
+        <v>0.007822430820377433</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19082,7 +18661,7 @@
         <v>99.0</v>
       </c>
       <c r="G14" s="22">
-        <v>0.008980866848887154</v>
+        <v>0.008995795443434047</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19103,7 +18682,7 @@
         <v>210.07692307692307</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0038071065989847717</v>
+        <v>0.0038134350249339984</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19124,7 +18703,7 @@
         <v>64.9908256880734</v>
       </c>
       <c r="G16" s="22">
-        <v>0.010640374853572823</v>
+        <v>0.010658061992764251</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19145,7 +18724,7 @@
         <v>99.98550724637681</v>
       </c>
       <c r="G17" s="22">
-        <v>0.006735650136665365</v>
+        <v>0.0067468465825755355</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19166,7 +18745,7 @@
         <v>42.54304635761589</v>
       </c>
       <c r="G18" s="22">
-        <v>0.014740335806325654</v>
+        <v>0.014764838173462403</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19176,18 +18755,18 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C19" s="15">
-        <v>6266</v>
+        <v>5716</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="20">
-        <v>32.635416666666664</v>
+        <v>31.58011049723757</v>
       </c>
       <c r="G19" s="22">
-        <v>0.018742678641155797</v>
+        <v>0.01769824973110394</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19208,7 +18787,7 @@
         <v>99.98245614035088</v>
       </c>
       <c r="G20" s="22">
-        <v>0.005564232721593128</v>
+        <v>0.005573481959518921</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19229,7 +18808,7 @@
         <v>69.98529411764706</v>
       </c>
       <c r="G21" s="22">
-        <v>0.006638032018742679</v>
+        <v>0.006649066197320817</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19250,7 +18829,7 @@
         <v>28.97841726618705</v>
       </c>
       <c r="G22" s="22">
-        <v>0.013568918391253416</v>
+        <v>0.013591473550405788</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19271,7 +18850,7 @@
         <v>84.02127659574468</v>
       </c>
       <c r="G23" s="22">
-        <v>0.004588051542366263</v>
+        <v>0.004595678106971741</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19292,7 +18871,7 @@
         <v>59.983333333333334</v>
       </c>
       <c r="G24" s="22">
-        <v>0.005857087075361187</v>
+        <v>0.005866823115283074</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19313,7 +18892,7 @@
         <v>69.91111111111111</v>
       </c>
       <c r="G25" s="22">
-        <v>0.004392815306520891</v>
+        <v>0.004400117336462305</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19334,7 +18913,7 @@
         <v>80.0</v>
       </c>
       <c r="G26" s="22">
-        <v>0.0029285435376805937</v>
+        <v>0.002933411557641537</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19355,7 +18934,7 @@
         <v>66.5</v>
       </c>
       <c r="G27" s="22">
-        <v>0.001952362358453729</v>
+        <v>0.001955607705094358</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19376,7 +18955,7 @@
         <v>33.0</v>
       </c>
       <c r="G28" s="22">
-        <v>0.0031237797735259665</v>
+        <v>0.003128972328150973</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19397,7 +18976,7 @@
         <v>60.0</v>
       </c>
       <c r="G29" s="22">
-        <v>0.0016595080046856697</v>
+        <v>0.0016622665493302043</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19418,7 +18997,7 @@
         <v>28.0</v>
       </c>
       <c r="G30" s="22">
-        <v>0.0024404529480671613</v>
+        <v>0.0024445096313679476</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19439,7 +19018,7 @@
         <v>26.0</v>
       </c>
       <c r="G31" s="22">
-        <v>0.0005857087075361187</v>
+        <v>0.0005866823115283074</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
